--- a/www/flightdata/xlsx/eoss-375.xlsx
+++ b/www/flightdata/xlsx/eoss-375.xlsx
@@ -4860,7 +4860,7 @@
         <v>26529.49</v>
       </c>
       <c r="I2">
-        <v>1023</v>
+        <v>673</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
